--- a/result/Table202602.xlsx
+++ b/result/Table202602.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -525,19 +525,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I2" t="n">
         <v>13.47</v>
       </c>
       <c r="J2" t="n">
-        <v>6.99</v>
+        <v>6.94</v>
       </c>
       <c r="K2" t="n">
-        <v>-48.11</v>
+        <v>-48.48</v>
       </c>
       <c r="L2" t="n">
-        <v>-48106.9</v>
+        <v>-48478.1</v>
       </c>
     </row>
     <row r="3">
@@ -566,7 +566,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -575,19 +575,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I3" t="n">
         <v>13.58</v>
       </c>
       <c r="J3" t="n">
-        <v>8.83</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>-34.98</v>
+        <v>-35.27</v>
       </c>
       <c r="L3" t="n">
-        <v>-34977.91</v>
+        <v>-35272.46</v>
       </c>
     </row>
     <row r="4">

--- a/result/Table202602.xlsx
+++ b/result/Table202602.xlsx
@@ -616,24 +616,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
         <v>25.01</v>
       </c>
       <c r="J4" t="n">
-        <v>31.96</v>
+        <v>31.69</v>
       </c>
       <c r="K4" t="n">
-        <v>27.79</v>
+        <v>26.71</v>
       </c>
       <c r="L4" t="n">
-        <v>27788.88</v>
+        <v>26709.32</v>
       </c>
     </row>
     <row r="5">
@@ -758,24 +758,24 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
         <v>21.87</v>
       </c>
       <c r="J7" t="n">
-        <v>20.7</v>
+        <v>19.32</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.35</v>
+        <v>-11.66</v>
       </c>
       <c r="L7" t="n">
-        <v>-5349.79</v>
+        <v>-11659.81</v>
       </c>
     </row>
     <row r="8">
@@ -854,24 +854,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="I9" t="n">
         <v>7.14</v>
       </c>
       <c r="J9" t="n">
-        <v>6.76</v>
+        <v>10.48</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.32</v>
+        <v>46.78</v>
       </c>
       <c r="L9" t="n">
-        <v>-5322.13</v>
+        <v>46778.71</v>
       </c>
     </row>
     <row r="10">
@@ -900,24 +900,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="I10" t="n">
         <v>8.130000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>7.59</v>
+        <v>7.11</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.64</v>
+        <v>-12.55</v>
       </c>
       <c r="L10" t="n">
-        <v>-6642.07</v>
+        <v>-12546.13</v>
       </c>
     </row>
     <row r="11">
@@ -946,24 +946,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I11" t="n">
         <v>73.18000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>74.87</v>
+        <v>72.67</v>
       </c>
       <c r="K11" t="n">
-        <v>2.31</v>
+        <v>-0.7</v>
       </c>
       <c r="L11" t="n">
-        <v>2309.37</v>
+        <v>-696.91</v>
       </c>
     </row>
     <row r="12">
@@ -1092,24 +1092,24 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I14" t="n">
         <v>6.71</v>
       </c>
       <c r="J14" t="n">
-        <v>7.08</v>
+        <v>6.64</v>
       </c>
       <c r="K14" t="n">
-        <v>5.51</v>
+        <v>-1.04</v>
       </c>
       <c r="L14" t="n">
-        <v>5514.16</v>
+        <v>-1043.22</v>
       </c>
     </row>
   </sheetData>

--- a/result/Table202602.xlsx
+++ b/result/Table202602.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -525,19 +525,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I2" t="n">
         <v>13.47</v>
       </c>
       <c r="J2" t="n">
-        <v>6.94</v>
+        <v>6.79</v>
       </c>
       <c r="K2" t="n">
-        <v>-48.48</v>
+        <v>-49.59</v>
       </c>
       <c r="L2" t="n">
-        <v>-48478.1</v>
+        <v>-49591.69</v>
       </c>
     </row>
     <row r="3">
@@ -566,7 +566,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -575,19 +575,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I3" t="n">
         <v>13.58</v>
       </c>
       <c r="J3" t="n">
-        <v>8.789999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>-35.27</v>
+        <v>-36.38</v>
       </c>
       <c r="L3" t="n">
-        <v>-35272.46</v>
+        <v>-36377.03</v>
       </c>
     </row>
     <row r="4">

--- a/result/Table202602.xlsx
+++ b/result/Table202602.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -525,19 +525,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I2" t="n">
         <v>13.47</v>
       </c>
       <c r="J2" t="n">
-        <v>6.79</v>
+        <v>6.25</v>
       </c>
       <c r="K2" t="n">
-        <v>-49.59</v>
+        <v>-53.6</v>
       </c>
       <c r="L2" t="n">
-        <v>-49591.69</v>
+        <v>-53600.59</v>
       </c>
     </row>
     <row r="3">
@@ -566,7 +566,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -575,19 +575,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I3" t="n">
         <v>13.58</v>
       </c>
       <c r="J3" t="n">
-        <v>8.640000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>-36.38</v>
+        <v>-39.47</v>
       </c>
       <c r="L3" t="n">
-        <v>-36377.03</v>
+        <v>-39469.81</v>
       </c>
     </row>
     <row r="4">

--- a/result/Table202602.xlsx
+++ b/result/Table202602.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -525,19 +525,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="I2" t="n">
         <v>13.47</v>
       </c>
       <c r="J2" t="n">
-        <v>6.25</v>
+        <v>6.18</v>
       </c>
       <c r="K2" t="n">
-        <v>-53.6</v>
+        <v>-54.12</v>
       </c>
       <c r="L2" t="n">
-        <v>-53600.59</v>
+        <v>-54120.27</v>
       </c>
     </row>
     <row r="3">
@@ -566,7 +566,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -575,19 +575,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="I3" t="n">
         <v>13.58</v>
       </c>
       <c r="J3" t="n">
-        <v>8.220000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="K3" t="n">
-        <v>-39.47</v>
+        <v>-39.99</v>
       </c>
       <c r="L3" t="n">
-        <v>-39469.81</v>
+        <v>-39985.27</v>
       </c>
     </row>
     <row r="4">
